--- a/Courses/Term 3/QAM-III/Case Studies/1430-1 DA.. DATA ABCL.. 24L GEOLOGIST MBA 2026.xlsx
+++ b/Courses/Term 3/QAM-III/Case Studies/1430-1 DA.. DATA ABCL.. 24L GEOLOGIST MBA 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suranjandas/Desktop/TEMP/Delhi EMBA............ B98 and B100/S6 - OR - BEFORE DA - 80 series/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MBA\Courses\Term 3\QAM-III\Case Studies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD21D85F-F38D-2448-9BC0-5C8A49CDD22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB948C1F-27CE-4804-858E-09A4001557A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="740" windowWidth="14000" windowHeight="13300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="problem" sheetId="4" r:id="rId1"/>
@@ -19,8 +19,19 @@
     <sheet name="Sheet3" sheetId="7" r:id="rId4"/>
     <sheet name="Sheet4" sheetId="3" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -2027,9 +2038,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="182.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="182.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -2042,10 +2053,10 @@
       <c r="H1" s="14"/>
       <c r="I1" s="14"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="12"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
     </row>
   </sheetData>
@@ -2065,7 +2076,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -2079,7 +2090,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -2093,7 +2104,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -2107,32 +2118,39 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:O27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="8.77734375" style="1"/>
     <col min="2" max="2" width="10.6640625" customWidth="1"/>
-    <col min="10" max="10" width="15.5" customWidth="1"/>
+    <col min="10" max="10" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J1" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C2" s="5"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C3" s="4"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="D4" s="8"/>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C3" s="4">
+        <f>$D$4*$J$4+$D$7*$J$7</f>
+        <v>940000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D4" s="8">
+        <v>0.6</v>
+      </c>
       <c r="E4" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="6"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="J4" s="6">
+        <v>1900000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>4</v>
       </c>
@@ -2140,25 +2158,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="N6" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="D7" s="8"/>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D7" s="8">
+        <v>0.4</v>
+      </c>
       <c r="E7" t="s">
         <v>2</v>
       </c>
-      <c r="J7" s="7"/>
+      <c r="J7" s="7">
+        <v>-500000</v>
+      </c>
       <c r="N7" s="8"/>
       <c r="O7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="F8" s="5"/>
-      <c r="G8" s="4"/>
+      <c r="G8" s="4">
+        <f>$H$9*$J$9+$H$12*$J$12</f>
+        <v>1540000</v>
+      </c>
       <c r="I8" t="s">
         <v>11</v>
       </c>
@@ -2167,15 +2192,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="H9" s="8"/>
-      <c r="J9" s="6"/>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="H9" s="8">
+        <v>0.85</v>
+      </c>
+      <c r="J9" s="6">
+        <v>1900000</v>
+      </c>
       <c r="N9" s="7"/>
       <c r="O9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="G10" t="s">
         <v>9</v>
@@ -2185,29 +2214,35 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
         <v>6</v>
       </c>
       <c r="E12" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="8"/>
+      <c r="H12" s="8">
+        <v>0.15</v>
+      </c>
       <c r="I12" t="s">
         <v>2</v>
       </c>
-      <c r="J12" s="7"/>
+      <c r="J12" s="7">
+        <v>-500000</v>
+      </c>
       <c r="N12" s="4"/>
       <c r="O12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C13" s="4"/>
-      <c r="D13" s="8"/>
+      <c r="D13" s="8">
+        <v>0.75</v>
+      </c>
       <c r="E13" t="s">
         <v>7</v>
       </c>
@@ -2216,67 +2251,89 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="G14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>5</v>
       </c>
       <c r="C15" t="s">
         <v>3</v>
       </c>
-      <c r="J15" s="7"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="J15" s="7">
+        <v>-500000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="5"/>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="18" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="H18" s="8"/>
+      <c r="G16" s="4">
+        <f>$H$12*$J$12</f>
+        <v>-75000</v>
+      </c>
+    </row>
+    <row r="18" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="H18" s="8">
+        <v>0.1</v>
+      </c>
       <c r="I18" t="s">
         <v>11</v>
       </c>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="J18" s="6">
+        <v>1900000</v>
+      </c>
+    </row>
+    <row r="19" spans="4:10" x14ac:dyDescent="0.3">
       <c r="F19" s="5"/>
-      <c r="G19" s="4"/>
-    </row>
-    <row r="21" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="G19" s="4">
+        <f>$H$18*$J$18+$J$23*$H$23</f>
+        <v>-260000</v>
+      </c>
+    </row>
+    <row r="21" spans="4:10" x14ac:dyDescent="0.3">
       <c r="E21" s="2"/>
       <c r="G21" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="4:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="4:10" x14ac:dyDescent="0.3">
       <c r="E22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="D23" s="8"/>
+    <row r="23" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="D23" s="8">
+        <v>0.15</v>
+      </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
-      <c r="H23" s="8"/>
+      <c r="H23" s="8">
+        <v>0.9</v>
+      </c>
       <c r="I23" t="s">
         <v>2</v>
       </c>
-      <c r="J23" s="7"/>
-    </row>
-    <row r="25" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="J23" s="7">
+        <v>-500000</v>
+      </c>
+    </row>
+    <row r="25" spans="4:10" x14ac:dyDescent="0.3">
       <c r="G25" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="J26" s="7"/>
-    </row>
-    <row r="27" spans="4:10" x14ac:dyDescent="0.2">
-      <c r="G27" s="4"/>
+    <row r="26" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="J26" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="G27" s="4">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
